--- a/NBFC-MF/Borrowers/Wangkheimayum_Thoibisana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Wangkheimayum_Thoibisana_Weekly.xlsx
@@ -929,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>296.77896817115123</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>1103.2210318288487</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>13697.569400122526</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>6302.4305998774744</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1126,7 +1128,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1161,7 +1163,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1196,7 +1198,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>14800.790431951375</v>
+        <v>13697.569400122526</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1231,7 +1233,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5199.2095680486254</v>
+        <v>6302.4305998774744</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
